--- a/Codigos/Windows/TF_HBI.xlsx
+++ b/Codigos/Windows/TF_HBI.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.0001708</v>
       </c>
     </row>
     <row r="5">
@@ -453,7 +453,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.0001708</v>
       </c>
     </row>
     <row r="6">
@@ -461,7 +461,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>0.0001708</v>
       </c>
     </row>
     <row r="7">
@@ -469,7 +469,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>0.0003416</v>
       </c>
     </row>
     <row r="8">
@@ -477,7 +477,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.0008541</v>
       </c>
     </row>
     <row r="9">
@@ -485,7 +485,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.0018791</v>
       </c>
     </row>
     <row r="10">
@@ -493,7 +493,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.0025624</v>
       </c>
     </row>
     <row r="11">
@@ -501,7 +501,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>0.0027332</v>
       </c>
     </row>
     <row r="12">
@@ -509,7 +509,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>0.0044414</v>
       </c>
     </row>
     <row r="13">
@@ -517,7 +517,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.007857899999999999</v>
       </c>
     </row>
     <row r="14">
@@ -525,7 +525,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.0254527</v>
       </c>
     </row>
     <row r="15">
@@ -533,7 +533,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.0644004</v>
       </c>
     </row>
     <row r="16">
@@ -541,7 +541,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0046232</v>
+        <v>0.1241886</v>
       </c>
     </row>
     <row r="17">
@@ -549,7 +549,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0131761</v>
+        <v>0.2126751</v>
       </c>
     </row>
     <row r="18">
@@ -557,7 +557,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0263523</v>
+        <v>0.3320806</v>
       </c>
     </row>
     <row r="19">
@@ -565,7 +565,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0423024</v>
+        <v>0.4465323</v>
       </c>
     </row>
     <row r="20">
@@ -573,7 +573,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0538604</v>
+        <v>0.5630338</v>
       </c>
     </row>
     <row r="21">
@@ -581,7 +581,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.0755895</v>
+        <v>0.6747523</v>
       </c>
     </row>
     <row r="22">
@@ -589,7 +589,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.1111882</v>
+        <v>0.7825419</v>
       </c>
     </row>
     <row r="23">
@@ -597,7 +597,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.1745261</v>
+        <v>0.8624872</v>
       </c>
     </row>
     <row r="24">
@@ -605,7 +605,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.2889505</v>
+        <v>0.917834</v>
       </c>
     </row>
     <row r="25">
@@ -613,7 +613,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.3982894</v>
+        <v>0.9496071</v>
       </c>
     </row>
     <row r="26">
@@ -621,7 +621,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.4720296</v>
+        <v>0.9665186</v>
       </c>
     </row>
     <row r="27">
@@ -629,7 +629,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.543227</v>
+        <v>0.971985</v>
       </c>
     </row>
     <row r="28">
@@ -637,7 +637,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.6257513</v>
+        <v>0.9743765</v>
       </c>
     </row>
     <row r="29">
@@ -645,7 +645,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.7004161</v>
+        <v>0.976768</v>
       </c>
     </row>
     <row r="30">
@@ -653,7 +653,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.7572816</v>
+        <v>0.9793304</v>
       </c>
     </row>
     <row r="31">
@@ -661,7 +661,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.809755</v>
+        <v>0.9844551</v>
       </c>
     </row>
     <row r="32">
@@ -669,7 +669,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>0.8469718000000001</v>
+        <v>0.9873591</v>
       </c>
     </row>
     <row r="33">
@@ -677,7 +677,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>0.8825705</v>
+        <v>0.9892381</v>
       </c>
     </row>
     <row r="34">
@@ -685,7 +685,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>0.9040684</v>
+        <v>0.9916296999999999</v>
       </c>
     </row>
     <row r="35">
@@ -693,7 +693,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>0.9234859</v>
+        <v>0.9936795</v>
       </c>
     </row>
     <row r="36">
@@ -701,7 +701,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>0.9410541</v>
+        <v>0.9952169</v>
       </c>
     </row>
     <row r="37">
@@ -709,7 +709,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>0.9565418</v>
+        <v>0.9965835</v>
       </c>
     </row>
     <row r="38">
@@ -717,7 +717,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>0.969718</v>
+        <v>0.9977793</v>
       </c>
     </row>
     <row r="39">
@@ -725,7 +725,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>0.9775774</v>
+        <v>0.9986334</v>
       </c>
     </row>
     <row r="40">
@@ -733,7 +733,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>0.987055</v>
+        <v>0.9996583999999999</v>
       </c>
     </row>
     <row r="41">
@@ -741,7 +741,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>0.9930652</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -749,7 +749,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>0.995608</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -757,7 +757,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>0.9963014</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -765,7 +765,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>0.9972261</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -773,7 +773,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>0.9976884</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -781,7 +781,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>0.9976884</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -789,7 +789,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>0.9990753999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -797,7 +797,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>0.9993065</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -805,7 +805,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>0.9997688</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -813,7 +813,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>0.9997688</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -821,7 +821,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>0.9997688</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -1061,6 +1061,166 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="n">
         <v>1</v>
       </c>
     </row>
